--- a/girlstars.xlsx
+++ b/girlstars.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ30"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -476,34 +476,33 @@
     <col width="58" customWidth="1" min="6" max="6"/>
     <col width="18.9" customWidth="1" min="7" max="7"/>
     <col width="13.7" customWidth="1" min="8" max="8"/>
-    <col width="16.3" customWidth="1" min="9" max="9"/>
-    <col width="17.6" customWidth="1" min="10" max="10"/>
-    <col width="22.8" customWidth="1" min="11" max="11"/>
-    <col width="18.9" customWidth="1" min="12" max="12"/>
-    <col width="21.5" customWidth="1" min="13" max="13"/>
-    <col width="20.2" customWidth="1" min="14" max="14"/>
+    <col width="13.7" customWidth="1" min="9" max="9"/>
+    <col width="20.2" customWidth="1" min="10" max="10"/>
+    <col width="17.6" customWidth="1" min="11" max="11"/>
+    <col width="22.8" customWidth="1" min="12" max="12"/>
+    <col width="16.3" customWidth="1" min="13" max="13"/>
+    <col width="18.9" customWidth="1" min="14" max="14"/>
     <col width="18.9" customWidth="1" min="15" max="15"/>
-    <col width="18.9" customWidth="1" min="16" max="16"/>
-    <col width="24.1" customWidth="1" min="17" max="17"/>
-    <col width="18.9" customWidth="1" min="18" max="18"/>
-    <col width="12.4" customWidth="1" min="19" max="19"/>
-    <col width="17.6" customWidth="1" min="20" max="20"/>
-    <col width="12.4" customWidth="1" min="21" max="21"/>
-    <col width="13.7" customWidth="1" min="22" max="22"/>
+    <col width="24.1" customWidth="1" min="16" max="16"/>
+    <col width="18.9" customWidth="1" min="17" max="17"/>
+    <col width="12.4" customWidth="1" min="18" max="18"/>
+    <col width="17.6" customWidth="1" min="19" max="19"/>
+    <col width="12.4" customWidth="1" min="20" max="20"/>
+    <col width="13.7" customWidth="1" min="21" max="21"/>
+    <col width="12.4" customWidth="1" min="22" max="22"/>
     <col width="12.4" customWidth="1" min="23" max="23"/>
-    <col width="12.4" customWidth="1" min="24" max="24"/>
-    <col width="15" customWidth="1" min="25" max="25"/>
-    <col width="16.3" customWidth="1" min="26" max="26"/>
-    <col width="18.9" customWidth="1" min="27" max="27"/>
-    <col width="24.1" customWidth="1" min="28" max="28"/>
-    <col width="12.4" customWidth="1" min="29" max="29"/>
-    <col width="22.8" customWidth="1" min="30" max="30"/>
-    <col width="26.7" customWidth="1" min="31" max="31"/>
-    <col width="11.1" customWidth="1" min="32" max="32"/>
-    <col width="18.9" customWidth="1" min="33" max="33"/>
-    <col width="22.8" customWidth="1" min="34" max="34"/>
-    <col width="11.1" customWidth="1" min="35" max="35"/>
-    <col width="20.2" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="16.3" customWidth="1" min="25" max="25"/>
+    <col width="18.9" customWidth="1" min="26" max="26"/>
+    <col width="21.5" customWidth="1" min="27" max="27"/>
+    <col width="12.4" customWidth="1" min="28" max="28"/>
+    <col width="22.8" customWidth="1" min="29" max="29"/>
+    <col width="26.7" customWidth="1" min="30" max="30"/>
+    <col width="20.2" customWidth="1" min="31" max="31"/>
+    <col width="18.9" customWidth="1" min="32" max="32"/>
+    <col width="22.8" customWidth="1" min="33" max="33"/>
+    <col width="11.1" customWidth="1" min="34" max="34"/>
+    <col width="20.2" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -682,11 +681,6 @@
           <t>數值（每個效果鍵一欄）</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>數值（每個效果鍵一欄）</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr"/>
@@ -722,145 +716,140 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>點錯一次不算（盤面與評價都不算、連擊不斷）；點對就重置</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>聖徒化期間全程指引下一格</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>無傷擊殺回填聖徒化</t>
-        </is>
-      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>發動彈雨傾洩回復主動技的使用次數</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
           <t>獄門天鎖免傷期間每發回復（佔最大體力）</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>反擊也算一發（回血窗）</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>魂之歸所延續聖徒化連擊增傷的秒數</t>
-        </is>
-      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>魂之歸所延續連擊增傷</t>
+          <t>單場無傷擊殺回復聖徒化熔斷</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>魂之歸所期間指引下一格</t>
+          <t>聖徒化發動時體力降至 1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>聖徒化發動時體力降至 1</t>
+          <t>獄門天鎖每一場戰鬥都可發動</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>獄門天鎖每一場戰鬥都可發動</t>
+          <t>受敵攻擊不推進倒數槽</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>受敵攻擊不推進倒數槽</t>
+          <t>聖徒化期間每發延長倒數（佔最大體力）</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>聖徒化期間每發延長倒數（佔最大體力）</t>
+          <t>夢魘化期間攻擊力**增量**（0.2＝×1.2）</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>夢魘化期間攻擊力**增量**（0.2＝×1.2）</t>
+          <t>夢境破碎後的反擊增益秒數</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>夢境破碎後的反擊增益秒數</t>
+          <t>該增益的攻擊力帶位（0黃 1橘 2紅，可累加）</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>該增益的攻擊力帶位（0黃 1橘 2紅，可累加）</t>
+          <t>該增益期間指引下一格</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>該增益期間指引下一格</t>
+          <t>連續三次完美反擊回填夢魘化</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>連續三次完美反擊回填夢魘化</t>
+          <t>明晰之夢秒數的**增量**（可累加）</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>明晰之夢秒數的**增量**（可累加）</t>
+          <t>明晰之夢期間的攻擊力帶位（0黃 1橘 2紅，可累加）</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>明晰之夢期間的攻擊力帶位（0黃 1橘 2紅，可累加）</t>
+          <t>夢魘化發動時體力先回滿</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>夢魘化發動時體力先回滿</t>
+          <t>最後一格夢境破碎的追加傷害（佔敵最大體力）</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>最後一格夢境破碎的追加傷害（佔敵最大體力）</t>
+          <t>霸王條款那一發**先從破防計扣**多少比例（0.3333＝1/3 表）</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>每次反擊讓夢魘化抽血暫停的秒數</t>
+          <t>彈雨傾洩攻擊力**增量**（0.2＝×1.2）</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>彈雨傾洩攻擊力**增量**（0.2＝×1.2）</t>
+          <t>獵手的戰吼發動時回填主動技</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>獵手的戰吼發動時回填主動技</t>
+          <t>主動技後破防值累積 200% 的秒數</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>主動技後破防值累積 200% 的秒數</t>
+          <t>共鬥飛刀的威力**增量**（基底＝一次普攻；0.5＝+50%，可累加）</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>共鬥自動反擊的攻擊力帶位（0黃 1橘 2紅，可累加）</t>
+          <t>戰吼所需連續完美清盤數的**減量**</t>
         </is>
       </c>
       <c r="AG2" s="2" t="inlineStr">
         <is>
-          <t>戰吼所需連續完美清盤數的**減量**</t>
+          <t>主動技發動同時回填共鬥</t>
         </is>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>主動技發動同時回填共鬥</t>
+          <t>共鬥最大持續時間的**增量**（秒）</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
-        <is>
-          <t>共鬥最大持續時間的**增量**（秒）</t>
-        </is>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>共鬥期間可累積破防值（＝延長時間）</t>
         </is>
@@ -904,145 +893,140 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>missGuard</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>saintHint</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>brReloadActive</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>guardHealPct</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>guardHealCounter</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>saintReload</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>guardHealPct</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>guardHealCounter</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>lifeReturnSec</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>lifeReturnCombo</t>
-        </is>
-      </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>lifeReturnHint</t>
+          <t>saintStartHp1</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>saintStartHp1</t>
+          <t>guardPerEnemy</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>guardPerEnemy</t>
+          <t>saintNoHitAdvance</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>saintNoHitAdvance</t>
+          <t>saintDrainPct</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>saintDrainPct</t>
+          <t>niDmgMul</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>niDmgMul</t>
+          <t>burstBuffSec</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>burstBuffSec</t>
+          <t>burstAtk</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>burstAtk</t>
+          <t>burstHint</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>burstHint</t>
+          <t>niReload</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>niReload</t>
+          <t>lucidSec</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>lucidSec</t>
+          <t>counterAtk</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>counterAtk</t>
+          <t>niFullStart</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>niFullStart</t>
+          <t>burstLastCell</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>burstLastCell</t>
+          <t>niCounterEnergy</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>niCounterPauseSec</t>
+          <t>brDmgMul</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>brDmgMul</t>
+          <t>roarReloadActive</t>
         </is>
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>roarReloadActive</t>
+          <t>activeEnergyBuffSec</t>
         </is>
       </c>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>activeEnergyBuffSec</t>
+          <t>coopCounterMul</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>coopAtk</t>
+          <t>roarStreakCut</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>roarStreakCut</t>
+          <t>activeReloadCoop</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>activeReloadCoop</t>
+          <t>coopSec</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
-        <is>
-          <t>coopSec</t>
-        </is>
-      </c>
-      <c r="AJ3" s="3" t="inlineStr">
         <is>
           <t>coopEnergyTime</t>
         </is>
@@ -1108,7 +1092,6 @@
       <c r="AG4" s="5" t="inlineStr"/>
       <c r="AH4" s="5" t="inlineStr"/>
       <c r="AI4" s="5" t="inlineStr"/>
-      <c r="AJ4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1121,12 +1104,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Guisuyi</t>
+          <t>Asellus Borealis</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>端首星</t>
+          <t>引路星</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1136,14 +1119,16 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>聖徒化期間全程指引下一格。</t>
+          <t>失誤一次不受擊，點擊正確就重置。並在聖徒化期間全程指引下一格。</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
       <c r="H5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="J5" s="5" t="inlineStr"/>
       <c r="K5" s="5" t="inlineStr"/>
       <c r="L5" s="5" t="inlineStr"/>
@@ -1170,7 +1155,6 @@
       <c r="AG5" s="5" t="inlineStr"/>
       <c r="AH5" s="5" t="inlineStr"/>
       <c r="AI5" s="5" t="inlineStr"/>
-      <c r="AJ5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1193,20 +1177,20 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>覺醒技</t>
+          <t>主動技</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>單場無傷擊殺即回填聖徒化。單場戰鬥不可連續使用，同戰役的次場戰鬥生效。</t>
+          <t>發動彈雨傾洩可回復魂之歸所的使用次數。</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
@@ -1232,7 +1216,6 @@
       <c r="AG6" s="5" t="inlineStr"/>
       <c r="AH6" s="5" t="inlineStr"/>
       <c r="AI6" s="5" t="inlineStr"/>
-      <c r="AJ6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1266,13 +1249,13 @@
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="L7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr"/>
       <c r="N7" s="5" t="inlineStr"/>
       <c r="O7" s="5" t="inlineStr"/>
@@ -1296,7 +1279,6 @@
       <c r="AG7" s="5" t="inlineStr"/>
       <c r="AH7" s="5" t="inlineStr"/>
       <c r="AI7" s="5" t="inlineStr"/>
-      <c r="AJ7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1309,22 +1291,22 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Asellus Borealis</t>
+          <t>Guisuyi</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>引路星</t>
+          <t>端首星</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>主動技</t>
+          <t>覺醒技</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>魂之歸所發動後 15 秒內延續聖徒化的連擊增傷，期間全程指引下一格。</t>
+          <t>單場無傷擊殺即回復聖徒化熔斷；同場戰鬥內不可連續使用。同戰役的次場戰鬥生效。</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -1332,15 +1314,11 @@
       <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="n">
-        <v>15</v>
-      </c>
+      <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="N8" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="N8" s="5" t="inlineStr"/>
       <c r="O8" s="5" t="inlineStr"/>
       <c r="P8" s="5" t="inlineStr"/>
       <c r="Q8" s="5" t="inlineStr"/>
@@ -1362,7 +1340,6 @@
       <c r="AG8" s="5" t="inlineStr"/>
       <c r="AH8" s="5" t="inlineStr"/>
       <c r="AI8" s="5" t="inlineStr"/>
-      <c r="AJ8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1400,10 +1377,10 @@
       <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="n">
+      <c r="N9" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="O9" s="5" t="inlineStr"/>
       <c r="P9" s="5" t="inlineStr"/>
       <c r="Q9" s="5" t="inlineStr"/>
       <c r="R9" s="5" t="inlineStr"/>
@@ -1424,7 +1401,6 @@
       <c r="AG9" s="5" t="inlineStr"/>
       <c r="AH9" s="5" t="inlineStr"/>
       <c r="AI9" s="5" t="inlineStr"/>
-      <c r="AJ9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1463,10 +1439,10 @@
       <c r="L10" s="5" t="inlineStr"/>
       <c r="M10" s="5" t="inlineStr"/>
       <c r="N10" s="5" t="inlineStr"/>
-      <c r="O10" s="5" t="inlineStr"/>
-      <c r="P10" s="5" t="n">
+      <c r="O10" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="P10" s="5" t="inlineStr"/>
       <c r="Q10" s="5" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr"/>
       <c r="S10" s="5" t="inlineStr"/>
@@ -1486,7 +1462,6 @@
       <c r="AG10" s="5" t="inlineStr"/>
       <c r="AH10" s="5" t="inlineStr"/>
       <c r="AI10" s="5" t="inlineStr"/>
-      <c r="AJ10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1526,10 +1501,10 @@
       <c r="M11" s="5" t="inlineStr"/>
       <c r="N11" s="5" t="inlineStr"/>
       <c r="O11" s="5" t="inlineStr"/>
-      <c r="P11" s="5" t="inlineStr"/>
-      <c r="Q11" s="5" t="n">
+      <c r="P11" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="Q11" s="5" t="inlineStr"/>
       <c r="R11" s="5" t="inlineStr"/>
       <c r="S11" s="5" t="inlineStr"/>
       <c r="T11" s="5" t="inlineStr"/>
@@ -1548,7 +1523,6 @@
       <c r="AG11" s="5" t="inlineStr"/>
       <c r="AH11" s="5" t="inlineStr"/>
       <c r="AI11" s="5" t="inlineStr"/>
-      <c r="AJ11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1589,10 +1563,10 @@
       <c r="N12" s="5" t="inlineStr"/>
       <c r="O12" s="5" t="inlineStr"/>
       <c r="P12" s="5" t="inlineStr"/>
-      <c r="Q12" s="5" t="inlineStr"/>
-      <c r="R12" s="5" t="n">
+      <c r="Q12" s="5" t="n">
         <v>0.01</v>
       </c>
+      <c r="R12" s="5" t="inlineStr"/>
       <c r="S12" s="5" t="inlineStr"/>
       <c r="T12" s="5" t="inlineStr"/>
       <c r="U12" s="5" t="inlineStr"/>
@@ -1610,7 +1584,6 @@
       <c r="AG12" s="5" t="inlineStr"/>
       <c r="AH12" s="5" t="inlineStr"/>
       <c r="AI12" s="5" t="inlineStr"/>
-      <c r="AJ12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1638,7 +1611,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>夢魘化期間的普攻與反擊攻擊力提升至 120%。</t>
+          <t>夢魘化期間反擊攻擊力提升至 120%。</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -1652,10 +1625,10 @@
       <c r="O13" s="5" t="inlineStr"/>
       <c r="P13" s="5" t="inlineStr"/>
       <c r="Q13" s="5" t="inlineStr"/>
-      <c r="R13" s="5" t="inlineStr"/>
-      <c r="S13" s="5" t="n">
+      <c r="R13" s="5" t="n">
         <v>0.2</v>
       </c>
+      <c r="S13" s="5" t="inlineStr"/>
       <c r="T13" s="5" t="inlineStr"/>
       <c r="U13" s="5" t="inlineStr"/>
       <c r="V13" s="5" t="inlineStr"/>
@@ -1672,7 +1645,6 @@
       <c r="AG13" s="5" t="inlineStr"/>
       <c r="AH13" s="5" t="inlineStr"/>
       <c r="AI13" s="5" t="inlineStr"/>
-      <c r="AJ13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1715,16 +1687,16 @@
       <c r="P14" s="5" t="inlineStr"/>
       <c r="Q14" s="5" t="inlineStr"/>
       <c r="R14" s="5" t="inlineStr"/>
-      <c r="S14" s="5" t="inlineStr"/>
+      <c r="S14" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="T14" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="U14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="V14" s="5" t="inlineStr"/>
       <c r="W14" s="5" t="inlineStr"/>
       <c r="X14" s="5" t="inlineStr"/>
       <c r="Y14" s="5" t="inlineStr"/>
@@ -1738,7 +1710,6 @@
       <c r="AG14" s="5" t="inlineStr"/>
       <c r="AH14" s="5" t="inlineStr"/>
       <c r="AI14" s="5" t="inlineStr"/>
-      <c r="AJ14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1766,7 +1737,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>連續三次完美反擊即回填夢魘化。單場戰鬥不可連續使用，同戰役的次場戰鬥生效。</t>
+          <t>連續三次完美反擊即回復夢魘化熔斷；同場戰鬥內不可連續使用。同戰役的次場戰鬥生效。</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -1784,10 +1755,10 @@
       <c r="S15" s="5" t="inlineStr"/>
       <c r="T15" s="5" t="inlineStr"/>
       <c r="U15" s="5" t="inlineStr"/>
-      <c r="V15" s="5" t="inlineStr"/>
-      <c r="W15" s="5" t="n">
+      <c r="V15" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="W15" s="5" t="inlineStr"/>
       <c r="X15" s="5" t="inlineStr"/>
       <c r="Y15" s="5" t="inlineStr"/>
       <c r="Z15" s="5" t="inlineStr"/>
@@ -1800,7 +1771,6 @@
       <c r="AG15" s="5" t="inlineStr"/>
       <c r="AH15" s="5" t="inlineStr"/>
       <c r="AI15" s="5" t="inlineStr"/>
-      <c r="AJ15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1847,13 +1817,13 @@
       <c r="T16" s="5" t="inlineStr"/>
       <c r="U16" s="5" t="inlineStr"/>
       <c r="V16" s="5" t="inlineStr"/>
-      <c r="W16" s="5" t="inlineStr"/>
+      <c r="W16" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="X16" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y16" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="Y16" s="5" t="inlineStr"/>
       <c r="Z16" s="5" t="inlineStr"/>
       <c r="AA16" s="5" t="inlineStr"/>
       <c r="AB16" s="5" t="inlineStr"/>
@@ -1864,7 +1834,6 @@
       <c r="AG16" s="5" t="inlineStr"/>
       <c r="AH16" s="5" t="inlineStr"/>
       <c r="AI16" s="5" t="inlineStr"/>
-      <c r="AJ16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1908,10 +1877,10 @@
       <c r="Q17" s="5" t="inlineStr"/>
       <c r="R17" s="5" t="inlineStr"/>
       <c r="S17" s="5" t="inlineStr"/>
-      <c r="T17" s="5" t="inlineStr"/>
-      <c r="U17" s="5" t="n">
+      <c r="T17" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="U17" s="5" t="inlineStr"/>
       <c r="V17" s="5" t="inlineStr"/>
       <c r="W17" s="5" t="inlineStr"/>
       <c r="X17" s="5" t="inlineStr"/>
@@ -1926,7 +1895,6 @@
       <c r="AG17" s="5" t="inlineStr"/>
       <c r="AH17" s="5" t="inlineStr"/>
       <c r="AI17" s="5" t="inlineStr"/>
-      <c r="AJ17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1975,10 +1943,10 @@
       <c r="V18" s="5" t="inlineStr"/>
       <c r="W18" s="5" t="inlineStr"/>
       <c r="X18" s="5" t="inlineStr"/>
-      <c r="Y18" s="5" t="inlineStr"/>
-      <c r="Z18" s="5" t="n">
+      <c r="Y18" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="Z18" s="5" t="inlineStr"/>
       <c r="AA18" s="5" t="inlineStr"/>
       <c r="AB18" s="5" t="inlineStr"/>
       <c r="AC18" s="5" t="inlineStr"/>
@@ -1988,7 +1956,6 @@
       <c r="AG18" s="5" t="inlineStr"/>
       <c r="AH18" s="5" t="inlineStr"/>
       <c r="AI18" s="5" t="inlineStr"/>
-      <c r="AJ18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2035,13 +2002,13 @@
       <c r="T19" s="5" t="inlineStr"/>
       <c r="U19" s="5" t="inlineStr"/>
       <c r="V19" s="5" t="inlineStr"/>
-      <c r="W19" s="5" t="inlineStr"/>
+      <c r="W19" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="X19" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y19" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="Y19" s="5" t="inlineStr"/>
       <c r="Z19" s="5" t="inlineStr"/>
       <c r="AA19" s="5" t="inlineStr"/>
       <c r="AB19" s="5" t="inlineStr"/>
@@ -2052,7 +2019,6 @@
       <c r="AG19" s="5" t="inlineStr"/>
       <c r="AH19" s="5" t="inlineStr"/>
       <c r="AI19" s="5" t="inlineStr"/>
-      <c r="AJ19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2102,10 +2068,10 @@
       <c r="W20" s="5" t="inlineStr"/>
       <c r="X20" s="5" t="inlineStr"/>
       <c r="Y20" s="5" t="inlineStr"/>
-      <c r="Z20" s="5" t="inlineStr"/>
-      <c r="AA20" s="5" t="n">
+      <c r="Z20" s="5" t="n">
         <v>0.3</v>
       </c>
+      <c r="AA20" s="5" t="inlineStr"/>
       <c r="AB20" s="5" t="inlineStr"/>
       <c r="AC20" s="5" t="inlineStr"/>
       <c r="AD20" s="5" t="inlineStr"/>
@@ -2114,7 +2080,6 @@
       <c r="AG20" s="5" t="inlineStr"/>
       <c r="AH20" s="5" t="inlineStr"/>
       <c r="AI20" s="5" t="inlineStr"/>
-      <c r="AJ20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2142,7 +2107,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>發動反擊可使夢魘化的體力流失減緩。</t>
+          <t>夢魘化期間發動反擊先消耗破防計，破防計耗盡才開始消耗體力。</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
@@ -2165,10 +2130,10 @@
       <c r="X21" s="5" t="inlineStr"/>
       <c r="Y21" s="5" t="inlineStr"/>
       <c r="Z21" s="5" t="inlineStr"/>
-      <c r="AA21" s="5" t="inlineStr"/>
-      <c r="AB21" s="5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="AA21" s="5" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AB21" s="5" t="inlineStr"/>
       <c r="AC21" s="5" t="inlineStr"/>
       <c r="AD21" s="5" t="inlineStr"/>
       <c r="AE21" s="5" t="inlineStr"/>
@@ -2176,7 +2141,6 @@
       <c r="AG21" s="5" t="inlineStr"/>
       <c r="AH21" s="5" t="inlineStr"/>
       <c r="AI21" s="5" t="inlineStr"/>
-      <c r="AJ21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2228,17 +2192,16 @@
       <c r="Y22" s="5" t="inlineStr"/>
       <c r="Z22" s="5" t="inlineStr"/>
       <c r="AA22" s="5" t="inlineStr"/>
-      <c r="AB22" s="5" t="inlineStr"/>
-      <c r="AC22" s="5" t="n">
+      <c r="AB22" s="5" t="n">
         <v>0.2</v>
       </c>
+      <c r="AC22" s="5" t="inlineStr"/>
       <c r="AD22" s="5" t="inlineStr"/>
       <c r="AE22" s="5" t="inlineStr"/>
       <c r="AF22" s="5" t="inlineStr"/>
       <c r="AG22" s="5" t="inlineStr"/>
       <c r="AH22" s="5" t="inlineStr"/>
       <c r="AI22" s="5" t="inlineStr"/>
-      <c r="AJ22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2291,16 +2254,15 @@
       <c r="Z23" s="5" t="inlineStr"/>
       <c r="AA23" s="5" t="inlineStr"/>
       <c r="AB23" s="5" t="inlineStr"/>
-      <c r="AC23" s="5" t="inlineStr"/>
-      <c r="AD23" s="5" t="n">
+      <c r="AC23" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="AD23" s="5" t="inlineStr"/>
       <c r="AE23" s="5" t="inlineStr"/>
       <c r="AF23" s="5" t="inlineStr"/>
       <c r="AG23" s="5" t="inlineStr"/>
       <c r="AH23" s="5" t="inlineStr"/>
       <c r="AI23" s="5" t="inlineStr"/>
-      <c r="AJ23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2354,15 +2316,14 @@
       <c r="AA24" s="5" t="inlineStr"/>
       <c r="AB24" s="5" t="inlineStr"/>
       <c r="AC24" s="5" t="inlineStr"/>
-      <c r="AD24" s="5" t="inlineStr"/>
-      <c r="AE24" s="5" t="n">
+      <c r="AD24" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="AE24" s="5" t="inlineStr"/>
       <c r="AF24" s="5" t="inlineStr"/>
       <c r="AG24" s="5" t="inlineStr"/>
       <c r="AH24" s="5" t="inlineStr"/>
       <c r="AI24" s="5" t="inlineStr"/>
-      <c r="AJ24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2390,7 +2351,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>獵手的共鬥期間，自動反擊攻擊力提升。</t>
+          <t>獵手的共鬥期間，自動反擊威力提升 50%。</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
@@ -2417,14 +2378,13 @@
       <c r="AB25" s="5" t="inlineStr"/>
       <c r="AC25" s="5" t="inlineStr"/>
       <c r="AD25" s="5" t="inlineStr"/>
-      <c r="AE25" s="5" t="inlineStr"/>
-      <c r="AF25" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE25" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF25" s="5" t="inlineStr"/>
       <c r="AG25" s="5" t="inlineStr"/>
       <c r="AH25" s="5" t="inlineStr"/>
       <c r="AI25" s="5" t="inlineStr"/>
-      <c r="AJ25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2480,13 +2440,12 @@
       <c r="AC26" s="5" t="inlineStr"/>
       <c r="AD26" s="5" t="inlineStr"/>
       <c r="AE26" s="5" t="inlineStr"/>
-      <c r="AF26" s="5" t="inlineStr"/>
-      <c r="AG26" s="5" t="n">
+      <c r="AF26" s="5" t="n">
         <v>2</v>
       </c>
+      <c r="AG26" s="5" t="inlineStr"/>
       <c r="AH26" s="5" t="inlineStr"/>
       <c r="AI26" s="5" t="inlineStr"/>
-      <c r="AJ26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2514,7 +2473,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>獵手的共鬥期間，自動反擊攻擊力提升。</t>
+          <t>獵手的共鬥期間，自動反擊威力再提升 100%。</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
@@ -2541,14 +2500,13 @@
       <c r="AB27" s="5" t="inlineStr"/>
       <c r="AC27" s="5" t="inlineStr"/>
       <c r="AD27" s="5" t="inlineStr"/>
-      <c r="AE27" s="5" t="inlineStr"/>
-      <c r="AF27" s="5" t="n">
+      <c r="AE27" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="AF27" s="5" t="inlineStr"/>
       <c r="AG27" s="5" t="inlineStr"/>
       <c r="AH27" s="5" t="inlineStr"/>
       <c r="AI27" s="5" t="inlineStr"/>
-      <c r="AJ27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2605,12 +2563,11 @@
       <c r="AD28" s="5" t="inlineStr"/>
       <c r="AE28" s="5" t="inlineStr"/>
       <c r="AF28" s="5" t="inlineStr"/>
-      <c r="AG28" s="5" t="inlineStr"/>
-      <c r="AH28" s="5" t="n">
+      <c r="AG28" s="5" t="n">
         <v>1</v>
       </c>
+      <c r="AH28" s="5" t="inlineStr"/>
       <c r="AI28" s="5" t="inlineStr"/>
-      <c r="AJ28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2668,11 +2625,10 @@
       <c r="AE29" s="5" t="inlineStr"/>
       <c r="AF29" s="5" t="inlineStr"/>
       <c r="AG29" s="5" t="inlineStr"/>
-      <c r="AH29" s="5" t="inlineStr"/>
-      <c r="AI29" s="5" t="n">
+      <c r="AH29" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="AJ29" s="5" t="inlineStr"/>
+      <c r="AI29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2731,8 +2687,7 @@
       <c r="AF30" s="5" t="inlineStr"/>
       <c r="AG30" s="5" t="inlineStr"/>
       <c r="AH30" s="5" t="inlineStr"/>
-      <c r="AI30" s="5" t="inlineStr"/>
-      <c r="AJ30" s="5" t="n">
+      <c r="AI30" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2834,7 +2789,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>發動方式：聖徒化期間戰鬥畫面上滑。 / 聖徒化期間發動，強制中止爆發時間，保留已回復之 HP。</t>
+          <t>發動方式：戰鬥畫面上滑。 / 一般時間發動：至本盤清盤為止，每次射擊回復最大體力 5%。 / 聖徒化期間發動：強制中止爆發時間，保留已回復之 HP。</t>
         </is>
       </c>
     </row>

--- a/girlstars.xlsx
+++ b/girlstars.xlsx
@@ -1564,7 +1564,7 @@
       <c r="O12" s="5" t="inlineStr"/>
       <c r="P12" s="5" t="inlineStr"/>
       <c r="Q12" s="5" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="R12" s="5" t="inlineStr"/>
       <c r="S12" s="5" t="inlineStr"/>
